--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -656,30 +656,30 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="3" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
     <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>23-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1142,125 +1142,77 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
+      </c>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
+      </c>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
       <c r="AK3" t="n">
         <v/>
@@ -1290,7 +1242,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1328,85 +1280,53 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
+      </c>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1460,7 +1380,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1498,85 +1418,53 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1630,7 +1518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1668,85 +1556,53 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1800,7 +1656,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1838,85 +1694,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1970,7 +1794,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2008,85 +1832,53 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2140,7 +1932,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2155,17 +1947,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2178,85 +1970,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2310,7 +2070,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27-March-2026</t>
+          <t>30-March-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2325,17 +2085,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2348,85 +2108,53 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -655,19 +655,19 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -902,197 +902,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>25-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>24-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1104,67 +1104,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
       <c r="S3" t="n">
         <v/>
@@ -1242,67 +1258,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
       <c r="S4" t="n">
         <v/>
@@ -1380,67 +1412,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
       <c r="S5" t="n">
         <v/>
@@ -1518,67 +1566,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
       <c r="S6" t="n">
         <v/>
@@ -1656,67 +1720,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
       <c r="S7" t="n">
         <v/>
@@ -1794,67 +1874,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
       <c r="S8" t="n">
         <v/>
@@ -1932,67 +2028,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
       </c>
       <c r="S9" t="n">
         <v/>
@@ -2070,67 +2182,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
       </c>
       <c r="S10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -664,19 +664,19 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,197 +902,197 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1104,107 +1104,123 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
-        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1258,107 +1274,123 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
-        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1412,107 +1444,123 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1566,107 +1614,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1720,107 +1784,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1874,107 +1954,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2028,107 +2124,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2182,107 +2294,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -673,7 +673,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -654,8 +654,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -654,29 +654,29 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1142,85 +1142,53 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
+      </c>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1274,7 +1242,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1312,85 +1280,53 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
+      </c>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1444,7 +1380,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1482,85 +1418,53 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1614,7 +1518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1652,85 +1556,53 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1784,7 +1656,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,85 +1694,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1954,7 +1794,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1992,85 +1832,53 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2124,7 +1932,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2139,12 +1947,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2162,85 +1970,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2294,7 +2070,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03-April-2026</t>
+          <t>06-April-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2309,7 +2085,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2319,7 +2095,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2332,85 +2108,53 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -661,13 +661,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,67 +1104,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
       <c r="S3" t="n">
         <v/>
@@ -1242,67 +1258,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
       <c r="S4" t="n">
         <v/>
@@ -1380,67 +1412,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
       <c r="S5" t="n">
         <v/>
@@ -1518,67 +1566,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
       <c r="S6" t="n">
         <v/>
@@ -1656,67 +1720,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
       <c r="S7" t="n">
         <v/>
@@ -1794,67 +1874,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
       <c r="S8" t="n">
         <v/>
@@ -1932,67 +2028,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
       </c>
       <c r="S9" t="n">
         <v/>
@@ -2070,67 +2182,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
       </c>
       <c r="S10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -670,13 +670,13 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,107 +1104,123 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
-        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1258,107 +1274,123 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
-        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1412,107 +1444,123 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1566,107 +1614,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1720,107 +1784,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1874,107 +1954,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2028,107 +2124,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2182,107 +2294,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,112 +2124,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1129</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -661,22 +661,22 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1142,85 +1142,53 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
+      </c>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1274,7 +1242,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1312,85 +1280,53 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
+      </c>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1444,7 +1380,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1482,85 +1418,53 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1614,7 +1518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1652,85 +1556,53 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1784,7 +1656,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,85 +1694,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1954,7 +1794,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1992,85 +1832,53 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2124,7 +1932,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2139,17 +1947,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2162,85 +1970,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2294,7 +2070,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10-April-2026</t>
+          <t>13-April-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2309,17 +2085,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>136</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2332,85 +2108,53 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -661,13 +661,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>07-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,67 +1104,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
       <c r="S3" t="n">
         <v/>
@@ -1242,67 +1258,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
       <c r="S4" t="n">
         <v/>
@@ -1380,67 +1412,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
       <c r="S5" t="n">
         <v/>
@@ -1518,67 +1566,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
       <c r="S6" t="n">
         <v/>
@@ -1656,67 +1720,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
       <c r="S7" t="n">
         <v/>
@@ -1794,67 +1874,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
       <c r="S8" t="n">
         <v/>
@@ -1932,67 +2028,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
       </c>
       <c r="S9" t="n">
         <v/>
@@ -2070,67 +2182,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>14-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
       </c>
       <c r="S10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -670,13 +670,13 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>08-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,107 +1104,123 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
-        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1258,107 +1274,123 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
-        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1412,107 +1444,123 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1566,107 +1614,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1720,107 +1784,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1874,107 +1954,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2028,107 +2124,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2182,107 +2294,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>10-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>09-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>13-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>10-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,107 +2294,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -661,22 +661,22 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="3" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>16-April-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15-April-2026</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>14-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>13-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1142,85 +1142,53 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
+      </c>
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
+        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1274,7 +1242,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1312,85 +1280,53 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
+      </c>
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
+        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1444,7 +1380,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1482,85 +1418,53 @@
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
+      </c>
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
+        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1614,7 +1518,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1652,85 +1556,53 @@
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
+      </c>
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
+        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1784,7 +1656,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,85 +1694,53 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
+        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1954,7 +1794,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1992,85 +1832,53 @@
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2124,7 +1932,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2139,7 +1947,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2149,98 +1957,66 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
+        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2294,7 +2070,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17-April-2026</t>
+          <t>20-April-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2309,7 +2085,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2319,7 +2095,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2332,85 +2108,53 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="J10" t="n">
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v/>
+      </c>
+      <c r="L10" t="n">
+        <v/>
+      </c>
+      <c r="M10" t="n">
+        <v/>
+      </c>
+      <c r="N10" t="n">
+        <v/>
+      </c>
+      <c r="O10" t="n">
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v/>
+      </c>
+      <c r="Q10" t="n">
+        <v/>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
+        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -661,13 +661,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
@@ -902,187 +902,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>14-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1104,67 +1104,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
       <c r="S3" t="n">
         <v/>
@@ -1242,67 +1258,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
       <c r="S4" t="n">
         <v/>
@@ -1380,67 +1412,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
       <c r="S5" t="n">
         <v/>
@@ -1518,67 +1566,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
       <c r="S6" t="n">
         <v/>
@@ -1656,67 +1720,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
       <c r="S7" t="n">
         <v/>
@@ -1794,67 +1874,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
       <c r="S8" t="n">
         <v/>
@@ -1932,67 +2028,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1125</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
       </c>
       <c r="S9" t="n">
         <v/>
@@ -2070,67 +2182,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
-        <v/>
       </c>
       <c r="S10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -670,13 +670,13 @@
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>15-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,107 +1104,123 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="S3" t="n">
-        <v/>
-      </c>
-      <c r="T3" t="n">
-        <v/>
-      </c>
-      <c r="U3" t="n">
-        <v/>
-      </c>
-      <c r="V3" t="n">
-        <v/>
-      </c>
-      <c r="W3" t="n">
-        <v/>
-      </c>
-      <c r="X3" t="n">
-        <v/>
-      </c>
-      <c r="Y3" t="n">
-        <v/>
-      </c>
-      <c r="Z3" t="n">
-        <v/>
       </c>
       <c r="AB3" t="n">
         <v/>
@@ -1258,107 +1274,123 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="S4" t="n">
-        <v/>
-      </c>
-      <c r="T4" t="n">
-        <v/>
-      </c>
-      <c r="U4" t="n">
-        <v/>
-      </c>
-      <c r="V4" t="n">
-        <v/>
-      </c>
-      <c r="W4" t="n">
-        <v/>
-      </c>
-      <c r="X4" t="n">
-        <v/>
-      </c>
-      <c r="Y4" t="n">
-        <v/>
-      </c>
-      <c r="Z4" t="n">
-        <v/>
       </c>
       <c r="AB4" t="n">
         <v/>
@@ -1412,107 +1444,123 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="S5" t="n">
-        <v/>
-      </c>
-      <c r="T5" t="n">
-        <v/>
-      </c>
-      <c r="U5" t="n">
-        <v/>
-      </c>
-      <c r="V5" t="n">
-        <v/>
-      </c>
-      <c r="W5" t="n">
-        <v/>
-      </c>
-      <c r="X5" t="n">
-        <v/>
-      </c>
-      <c r="Y5" t="n">
-        <v/>
-      </c>
-      <c r="Z5" t="n">
-        <v/>
       </c>
       <c r="AB5" t="n">
         <v/>
@@ -1566,107 +1614,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="S6" t="n">
-        <v/>
-      </c>
-      <c r="T6" t="n">
-        <v/>
-      </c>
-      <c r="U6" t="n">
-        <v/>
-      </c>
-      <c r="V6" t="n">
-        <v/>
-      </c>
-      <c r="W6" t="n">
-        <v/>
-      </c>
-      <c r="X6" t="n">
-        <v/>
-      </c>
-      <c r="Y6" t="n">
-        <v/>
-      </c>
-      <c r="Z6" t="n">
-        <v/>
       </c>
       <c r="AB6" t="n">
         <v/>
@@ -1720,107 +1784,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
-        <v/>
       </c>
       <c r="AB7" t="n">
         <v/>
@@ -1874,107 +1954,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
-        <v/>
       </c>
       <c r="AB8" t="n">
         <v/>
@@ -2028,107 +2124,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1125</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2182,107 +2294,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,104 +2124,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>84</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,87 +1104,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1274,87 +1274,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1444,87 +1444,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1614,87 +1614,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1784,87 +1784,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1954,87 +1954,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -2124,87 +2124,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2294,112 +2294,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -156,6 +156,131 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -448,53 +573,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="3" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="3" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="4" customWidth="1" min="31" max="31"/>
-    <col width="4" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
-    <col width="3" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
-    <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="5" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
-    <col width="4" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="3" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,364 +627,254 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-April-2026</t>
+          <t>01-May-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>30</t>
         </is>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -271,6 +271,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -573,17 +598,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,53 +661,133 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -710,12 +824,36 @@
         <is>
           <t>35</t>
         </is>
+      </c>
+      <c r="J3" t="n">
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v/>
+      </c>
+      <c r="M3" t="n">
+        <v/>
+      </c>
+      <c r="N3" t="n">
+        <v/>
+      </c>
+      <c r="O3" t="n">
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v/>
+      </c>
+      <c r="Q3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -752,12 +890,36 @@
         <is>
           <t>22</t>
         </is>
+      </c>
+      <c r="J4" t="n">
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v/>
+      </c>
+      <c r="L4" t="n">
+        <v/>
+      </c>
+      <c r="M4" t="n">
+        <v/>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
+      <c r="O4" t="n">
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v/>
+      </c>
+      <c r="Q4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -794,12 +956,36 @@
         <is>
           <t>23</t>
         </is>
+      </c>
+      <c r="J5" t="n">
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v/>
+      </c>
+      <c r="M5" t="n">
+        <v/>
+      </c>
+      <c r="N5" t="n">
+        <v/>
+      </c>
+      <c r="O5" t="n">
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -814,17 +1000,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>351</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -836,48 +1022,162 @@
         <is>
           <t>12</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v/>
+      </c>
+      <c r="L6" t="n">
+        <v/>
+      </c>
+      <c r="M6" t="n">
+        <v/>
+      </c>
+      <c r="N6" t="n">
+        <v/>
+      </c>
+      <c r="O6" t="n">
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -611,13 +611,13 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,479 +705,575 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -598,15 +598,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -618,6 +618,15 @@
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +710,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -787,80 +876,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -869,80 +998,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -951,80 +1120,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1033,80 +1242,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1115,80 +1364,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1197,80 +1486,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>30</t>
         </is>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -598,24 +598,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -627,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,859 +759,1051 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v/>
+      </c>
+      <c r="B7" t="n">
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v/>
+      </c>
+      <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
+        <v/>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -612,19 +612,19 @@
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
@@ -803,129 +803,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>dsl</t>
@@ -938,17 +938,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -965,87 +965,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1111,87 +1111,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1257,87 +1257,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1403,87 +1403,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1571,69 +1571,53 @@
       <c r="H7" t="n">
         <v/>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>1130</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1701,74 +1685,58 @@
       <c r="H8" t="n">
         <v/>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v/>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>171</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -246,6 +246,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -548,20 +598,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
@@ -655,346 +705,542 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>08-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v/>
+      </c>
+      <c r="L7" t="n">
+        <v/>
+      </c>
+      <c r="M7" t="n">
+        <v/>
+      </c>
+      <c r="N7" t="n">
+        <v/>
+      </c>
+      <c r="O7" t="n">
+        <v/>
+      </c>
+      <c r="P7" t="n">
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v/>
+      </c>
+      <c r="L8" t="n">
+        <v/>
+      </c>
+      <c r="M8" t="n">
+        <v/>
+      </c>
+      <c r="N8" t="n">
+        <v/>
+      </c>
+      <c r="O8" t="n">
+        <v/>
+      </c>
+      <c r="P8" t="n">
+        <v/>
+      </c>
+      <c r="Q8" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -306,6 +306,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -598,26 +648,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,84 +760,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>895</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -787,80 +926,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -869,80 +1048,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -951,80 +1170,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1033,80 +1292,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1115,132 +1414,318 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>13-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -662,21 +662,30 @@
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -800,932 +809,1228 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>394</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v/>
-      </c>
-      <c r="T7" t="n">
-        <v/>
-      </c>
-      <c r="U7" t="n">
-        <v/>
-      </c>
-      <c r="V7" t="n">
-        <v/>
-      </c>
-      <c r="W7" t="n">
-        <v/>
-      </c>
-      <c r="X7" t="n">
-        <v/>
-      </c>
-      <c r="Y7" t="n">
-        <v/>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>418</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v/>
-      </c>
-      <c r="T8" t="n">
-        <v/>
-      </c>
-      <c r="U8" t="n">
-        <v/>
-      </c>
-      <c r="V8" t="n">
-        <v/>
-      </c>
-      <c r="W8" t="n">
-        <v/>
-      </c>
-      <c r="X8" t="n">
-        <v/>
-      </c>
-      <c r="Y8" t="n">
-        <v/>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>14-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -331,31 +331,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -671,11 +646,11 @@
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
@@ -853,142 +828,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>dsl</t>
+          <t>idrepo</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -998,7 +973,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>394</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1008,119 +983,119 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>394</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1161,87 +1136,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1307,87 +1282,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1453,87 +1428,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1599,87 +1574,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13-May-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1745,122 +1720,122 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1891,112 +1866,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>15-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>14-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>13-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>12-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -631,9 +631,18 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,44 +686,124 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -723,40 +812,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -765,40 +894,80 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -807,40 +976,80 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -849,40 +1058,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -891,40 +1140,80 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -933,82 +1222,146 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v/>
+      </c>
+      <c r="B9" t="n">
+        <v/>
+      </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -640,9 +640,18 @@
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,84 +735,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>486</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -812,80 +901,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -894,80 +1023,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -976,80 +1145,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -1058,80 +1267,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1140,162 +1389,226 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v/>
+      </c>
+      <c r="B8" t="n">
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
+        <v/>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1326,42 +1639,66 @@
       <c r="H9" t="n">
         <v/>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -306,31 +306,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>154</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -623,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -631,18 +606,18 @@
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -652,6 +627,15 @@
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,933 +759,1083 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>19-May-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18-May-2026</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="AB3" t="n">
+        <v/>
+      </c>
+      <c r="AC3" t="n">
+        <v/>
+      </c>
+      <c r="AD3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" t="n">
+        <v/>
+      </c>
+      <c r="AF3" t="n">
+        <v/>
+      </c>
+      <c r="AG3" t="n">
+        <v/>
+      </c>
+      <c r="AH3" t="n">
+        <v/>
+      </c>
+      <c r="AI3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
-      <c r="B8" t="n">
-        <v/>
-      </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>20-May-2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v/>
-      </c>
-      <c r="B9" t="n">
-        <v/>
-      </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
-      <c r="G9" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/dev11.xlsx
+++ b/minio-report-tracker/xlxs/dev11.xlsx
@@ -306,6 +306,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -598,15 +623,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
@@ -615,27 +640,18 @@
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="5" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -759,1082 +775,948 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v/>
-      </c>
-      <c r="AC3" t="n">
-        <v/>
-      </c>
-      <c r="AD3" t="n">
-        <v/>
-      </c>
-      <c r="AE3" t="n">
-        <v/>
-      </c>
-      <c r="AF3" t="n">
-        <v/>
-      </c>
-      <c r="AG3" t="n">
-        <v/>
-      </c>
-      <c r="AH3" t="n">
-        <v/>
-      </c>
-      <c r="AI3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>351</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>19-May-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v/>
       </c>
-      <c r="AC8" t="n">
+      <c r="K9" t="n">
         <v/>
       </c>
-      <c r="AD8" t="n">
+      <c r="L9" t="n">
         <v/>
       </c>
-      <c r="AE8" t="n">
+      <c r="M9" t="n">
         <v/>
       </c>
-      <c r="AF8" t="n">
+      <c r="N9" t="n">
         <v/>
       </c>
-      <c r="AG8" t="n">
+      <c r="O9" t="n">
         <v/>
       </c>
-      <c r="AH8" t="n">
+      <c r="P9" t="n">
         <v/>
       </c>
-      <c r="AI8" t="n">
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>
